--- a/publication_tables/supplementary/S18_coverage_conditional_intervals.xlsx
+++ b/publication_tables/supplementary/S18_coverage_conditional_intervals.xlsx
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.001912029532528728</v>
+        <v>-0.00195063297787698</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09336637906348963</v>
+        <v>-0.09342317200476444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0517417731581927</v>
+        <v>0.05165528253393076</v>
       </c>
       <c r="F2" t="n">
         <v>1000</v>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3721546348444293</v>
+        <v>-0.372041187632305</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5965882810315656</v>
+        <v>-0.5963362621943133</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1744837256962413</v>
+        <v>-0.1744745738179868</v>
       </c>
       <c r="F3" t="n">
         <v>1000</v>
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.6626795609870827</v>
+        <v>-0.6626162364829336</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9166927591008991</v>
+        <v>-0.9165348141215042</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4463372289499384</v>
+        <v>-0.4465778140696234</v>
       </c>
       <c r="F4" t="n">
         <v>1000</v>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.050307851082161</v>
+        <v>-1.050269592387097</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.313589362941825</v>
+        <v>-1.313566292814869</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8195090247916926</v>
+        <v>-0.8194720860255572</v>
       </c>
       <c r="F5" t="n">
         <v>1000</v>
@@ -584,7 +584,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>First fixed candidate in the paired conditional comparison. minimum_gap=4.3057268666% coverage; nearby_minimum=3.954934% coverage.</t>
+          <t>First fixed candidate in the paired conditional comparison. minimum_gap is the refined CES optimum; nearby_minimum is the preliminary CES candidate.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Second fixed candidate: pmt_20 or pmt_40 is exact 20% or 40% coverage; universal_cash is 100%; nearby_minimum is 3.954934%.</t>
+          <t>Second fixed candidate: pmt_20 or pmt_40 is exact 20% or 40% coverage; universal_cash is 100%; nearby_minimum is the preliminary CES candidate.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
